--- a/data/rme_plate_normalization_for_pcr.xlsx
+++ b/data/rme_plate_normalization_for_pcr.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/!students/Labrador_Dissertation/09_github-repositories/2026_labrador_preservation-of-edna-from-remote-areas/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="494" documentId="11_F25DC773A252ABDACC104819619D540C5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F57CB84C-F712-45D5-9824-7CB713C5BC11}"/>
+  <xr:revisionPtr revIDLastSave="496" documentId="11_F25DC773A252ABDACC104819619D540C5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87BE81A1-A3F1-4C08-9F9E-C653E55A31F7}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="normalized_plate_tidy" sheetId="3" r:id="rId2"/>
-    <sheet name="plate_layout" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">normalized_plate_tidy!$A$1:$Q$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="200">
   <si>
     <t>dna_plate_id</t>
   </si>
@@ -642,75 +639,13 @@
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>PCR Plate Map</t>
-  </si>
-  <si>
-    <t>Plate containing only samples from the first extractions</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> (rme = filter, rmep = preservative, PCR-NTC = PCR no template controls, ctrl_01 - 02 = mpH20 during rmep extractions, PC = </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Chaetodon tinkeri</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>ctrl_02</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>ctrl_01</t>
-  </si>
-  <si>
-    <t>PCR-NTC1</t>
-  </si>
-  <si>
-    <t>PCR-NTC3</t>
-  </si>
-  <si>
-    <t>PCR-NTC2</t>
-  </si>
-  <si>
-    <t>PCR-NTC4</t>
-  </si>
-  <si>
-    <t>rme_dna_for_pcr_normalized</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.tinkeri </t>
-  </si>
-  <si>
-    <t>mpH2O</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -726,30 +661,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -772,35 +693,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -828,15 +725,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8543,4459 +8431,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="57" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10C50BE-D82B-4376-8B52-5947BC365404}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Q82"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
-  <cols>
-    <col min="1" max="1" width="25.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.40625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="16" width="26.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="59" x14ac:dyDescent="0.75">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A2" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0.111967185</v>
-      </c>
-      <c r="I2" s="10">
-        <v>15</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K2" s="9">
-        <v>10</v>
-      </c>
-      <c r="L2" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M2" s="9">
-        <v>22.327970467418645</v>
-      </c>
-      <c r="N2" s="9">
-        <v>15</v>
-      </c>
-      <c r="O2" s="9">
-        <v>1.679507775</v>
-      </c>
-      <c r="P2" s="9">
-        <v>0.16795077750000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A3" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="9">
-        <v>0.146992238</v>
-      </c>
-      <c r="I3" s="10">
-        <v>15</v>
-      </c>
-      <c r="J3" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K3" s="9">
-        <v>10</v>
-      </c>
-      <c r="L3" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M3" s="9">
-        <v>17.007700773968761</v>
-      </c>
-      <c r="N3" s="9">
-        <v>15</v>
-      </c>
-      <c r="O3" s="9">
-        <v>2.2048835699999998</v>
-      </c>
-      <c r="P3" s="9">
-        <v>0.22048835699999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A4" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0.15511694000000001</v>
-      </c>
-      <c r="I4" s="10">
-        <v>15</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K4" s="9">
-        <v>10</v>
-      </c>
-      <c r="L4" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M4" s="9">
-        <v>16.116872857342337</v>
-      </c>
-      <c r="N4" s="9">
-        <v>15</v>
-      </c>
-      <c r="O4" s="9">
-        <v>2.3267541</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0.23267541</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A5" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="9">
-        <v>7.5420702000000006E-2</v>
-      </c>
-      <c r="I5" s="10">
-        <v>15</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K5" s="9">
-        <v>10</v>
-      </c>
-      <c r="L5" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M5" s="9">
-        <v>33.147397646868889</v>
-      </c>
-      <c r="N5" s="9">
-        <v>15</v>
-      </c>
-      <c r="O5" s="9">
-        <v>1.1313105300000001</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0.11313105300000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A6" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="9">
-        <v>0.41048947600000002</v>
-      </c>
-      <c r="I6" s="10">
-        <v>15</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K6" s="9">
-        <v>10</v>
-      </c>
-      <c r="L6" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M6" s="9">
-        <v>6.0902901198860455</v>
-      </c>
-      <c r="N6" s="9">
-        <v>6.0902901198860455</v>
-      </c>
-      <c r="O6" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A7" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="9">
-        <v>6.4041946000000002E-2</v>
-      </c>
-      <c r="I7" s="10">
-        <v>15</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K7" s="9">
-        <v>10</v>
-      </c>
-      <c r="L7" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M7" s="9">
-        <v>39.036914961953215</v>
-      </c>
-      <c r="N7" s="9">
-        <v>15</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0.96062919000000002</v>
-      </c>
-      <c r="P7" s="9">
-        <v>9.6062918999999997E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A8" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="9">
-        <v>4.1299289000000003E-2</v>
-      </c>
-      <c r="I8" s="10">
-        <v>15</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K8" s="9">
-        <v>10</v>
-      </c>
-      <c r="L8" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M8" s="9">
-        <v>60.533729769536706</v>
-      </c>
-      <c r="N8" s="9">
-        <v>15</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0.61948933500000003</v>
-      </c>
-      <c r="P8" s="9">
-        <v>6.1948933500000004E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A9" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="9">
-        <v>8.0900886000000005E-2</v>
-      </c>
-      <c r="I9" s="10">
-        <v>15</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K9" s="9">
-        <v>10</v>
-      </c>
-      <c r="L9" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M9" s="9">
-        <v>30.902010146094071</v>
-      </c>
-      <c r="N9" s="9">
-        <v>15</v>
-      </c>
-      <c r="O9" s="9">
-        <v>1.2135132900000001</v>
-      </c>
-      <c r="P9" s="9">
-        <v>0.12135132900000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A10" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0.37331788100000002</v>
-      </c>
-      <c r="I10" s="10">
-        <v>15</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K10" s="9">
-        <v>10</v>
-      </c>
-      <c r="L10" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M10" s="9">
-        <v>6.6967057492753739</v>
-      </c>
-      <c r="N10" s="9">
-        <v>6.6967057492753739</v>
-      </c>
-      <c r="O10" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P10" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A11" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="8">
-        <v>2</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0.41998344599999998</v>
-      </c>
-      <c r="I11" s="10">
-        <v>15</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K11" s="9">
-        <v>10</v>
-      </c>
-      <c r="L11" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M11" s="9">
-        <v>5.9526155704717949</v>
-      </c>
-      <c r="N11" s="9">
-        <v>5.9526155704717949</v>
-      </c>
-      <c r="O11" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P11" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A12" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="8">
-        <v>2</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0.54085449100000005</v>
-      </c>
-      <c r="I12" s="10">
-        <v>15</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K12" s="9">
-        <v>10</v>
-      </c>
-      <c r="L12" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M12" s="9">
-        <v>4.6223153206654244</v>
-      </c>
-      <c r="N12" s="9">
-        <v>4.6223153206654244</v>
-      </c>
-      <c r="O12" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P12" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A13" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="8">
-        <v>2</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A14" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="8">
-        <v>2</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H14" s="9">
-        <v>7.8858040000000004E-2</v>
-      </c>
-      <c r="I14" s="10">
-        <v>15</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K14" s="9">
-        <v>10</v>
-      </c>
-      <c r="L14" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M14" s="9">
-        <v>31.702537876924151</v>
-      </c>
-      <c r="N14" s="9">
-        <v>15</v>
-      </c>
-      <c r="O14" s="9">
-        <v>1.1828706</v>
-      </c>
-      <c r="P14" s="9">
-        <v>0.11828706</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A15" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="8">
-        <v>2</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="9">
-        <v>0.48919945100000001</v>
-      </c>
-      <c r="I15" s="10">
-        <v>15</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K15" s="9">
-        <v>10</v>
-      </c>
-      <c r="L15" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M15" s="9">
-        <v>5.1103900359855476</v>
-      </c>
-      <c r="N15" s="9">
-        <v>5.1103900359855476</v>
-      </c>
-      <c r="O15" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P15" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A16" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="8">
-        <v>2</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="9">
-        <v>1.9407611000000002E-2</v>
-      </c>
-      <c r="I16" s="10">
-        <v>15</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K16" s="9">
-        <v>10</v>
-      </c>
-      <c r="L16" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M16" s="9">
-        <v>128.81544256013785</v>
-      </c>
-      <c r="N16" s="9">
-        <v>15</v>
-      </c>
-      <c r="O16" s="9">
-        <v>0.29111416500000004</v>
-      </c>
-      <c r="P16" s="9">
-        <v>2.9111416500000004E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A17" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="8">
-        <v>2</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="9">
-        <v>1.7357727E-2</v>
-      </c>
-      <c r="I17" s="10">
-        <v>15</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K17" s="9">
-        <v>10</v>
-      </c>
-      <c r="L17" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M17" s="9">
-        <v>144.02807464364429</v>
-      </c>
-      <c r="N17" s="9">
-        <v>15</v>
-      </c>
-      <c r="O17" s="9">
-        <v>0.26036590500000001</v>
-      </c>
-      <c r="P17" s="9">
-        <v>2.6036590500000002E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A18" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F18" s="8">
-        <v>3</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="9">
-        <v>9.1340088999999999E-2</v>
-      </c>
-      <c r="I18" s="10">
-        <v>15</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K18" s="9">
-        <v>10</v>
-      </c>
-      <c r="L18" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M18" s="9">
-        <v>27.370238275112694</v>
-      </c>
-      <c r="N18" s="9">
-        <v>15</v>
-      </c>
-      <c r="O18" s="9">
-        <v>1.370101335</v>
-      </c>
-      <c r="P18" s="9">
-        <v>0.13701013349999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A19" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="8">
-        <v>3</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="9">
-        <v>7.8024336E-2</v>
-      </c>
-      <c r="I19" s="10">
-        <v>15</v>
-      </c>
-      <c r="J19" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K19" s="9">
-        <v>10</v>
-      </c>
-      <c r="L19" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M19" s="9">
-        <v>32.041285170308917</v>
-      </c>
-      <c r="N19" s="9">
-        <v>15</v>
-      </c>
-      <c r="O19" s="9">
-        <v>1.1703650400000001</v>
-      </c>
-      <c r="P19" s="9">
-        <v>0.11703650400000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A20" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="8">
-        <v>3</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0.13873068399999999</v>
-      </c>
-      <c r="I20" s="10">
-        <v>15</v>
-      </c>
-      <c r="J20" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K20" s="9">
-        <v>10</v>
-      </c>
-      <c r="L20" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M20" s="9">
-        <v>18.020526735094883</v>
-      </c>
-      <c r="N20" s="9">
-        <v>15</v>
-      </c>
-      <c r="O20" s="9">
-        <v>2.0809602599999999</v>
-      </c>
-      <c r="P20" s="9">
-        <v>0.20809602599999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A21" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="8">
-        <v>3</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" s="9">
-        <v>7.1803684000000007E-2</v>
-      </c>
-      <c r="I21" s="10">
-        <v>15</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K21" s="9">
-        <v>10</v>
-      </c>
-      <c r="L21" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M21" s="9">
-        <v>34.817155064077213</v>
-      </c>
-      <c r="N21" s="9">
-        <v>15</v>
-      </c>
-      <c r="O21" s="9">
-        <v>1.0770552600000001</v>
-      </c>
-      <c r="P21" s="9">
-        <v>0.10770552600000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A22" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="8">
-        <v>3</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="9">
-        <v>4.9747528999999999E-2</v>
-      </c>
-      <c r="I22" s="10">
-        <v>15</v>
-      </c>
-      <c r="J22" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K22" s="9">
-        <v>10</v>
-      </c>
-      <c r="L22" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M22" s="9">
-        <v>50.253752301948509</v>
-      </c>
-      <c r="N22" s="9">
-        <v>15</v>
-      </c>
-      <c r="O22" s="9">
-        <v>0.74621293499999997</v>
-      </c>
-      <c r="P22" s="9">
-        <v>7.4621293499999991E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A23" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="8">
-        <v>4</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="9">
-        <v>7.4428860999999999E-2</v>
-      </c>
-      <c r="I23" s="10">
-        <v>15</v>
-      </c>
-      <c r="J23" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K23" s="9">
-        <v>10</v>
-      </c>
-      <c r="L23" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M23" s="9">
-        <v>33.589120757873751</v>
-      </c>
-      <c r="N23" s="9">
-        <v>15</v>
-      </c>
-      <c r="O23" s="9">
-        <v>1.1164329150000001</v>
-      </c>
-      <c r="P23" s="9">
-        <v>0.11164329150000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A24" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="8">
-        <v>5</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H24" s="9">
-        <v>8.5283949999999997E-2</v>
-      </c>
-      <c r="I24" s="10">
-        <v>15</v>
-      </c>
-      <c r="J24" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K24" s="9">
-        <v>10</v>
-      </c>
-      <c r="L24" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M24" s="9">
-        <v>29.313839239387953</v>
-      </c>
-      <c r="N24" s="9">
-        <v>15</v>
-      </c>
-      <c r="O24" s="9">
-        <v>1.27925925</v>
-      </c>
-      <c r="P24" s="9">
-        <v>0.127925925</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A25" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" s="8">
-        <v>5</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H25" s="9">
-        <v>6.9987299000000003E-2</v>
-      </c>
-      <c r="I25" s="10">
-        <v>15</v>
-      </c>
-      <c r="J25" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K25" s="9">
-        <v>10</v>
-      </c>
-      <c r="L25" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M25" s="9">
-        <v>35.720766992308128</v>
-      </c>
-      <c r="N25" s="9">
-        <v>15</v>
-      </c>
-      <c r="O25" s="9">
-        <v>1.0498094849999999</v>
-      </c>
-      <c r="P25" s="9">
-        <v>0.10498094849999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A26" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="8">
-        <v>4</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" s="9">
-        <v>4.0607135000000003E-2</v>
-      </c>
-      <c r="I26" s="10">
-        <v>15</v>
-      </c>
-      <c r="J26" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K26" s="9">
-        <v>10</v>
-      </c>
-      <c r="L26" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M26" s="9">
-        <v>61.565535219364769</v>
-      </c>
-      <c r="N26" s="9">
-        <v>15</v>
-      </c>
-      <c r="O26" s="9">
-        <v>0.60910702500000002</v>
-      </c>
-      <c r="P26" s="9">
-        <v>6.0910702500000004E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A27" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="8">
-        <v>5</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H27" s="9">
-        <v>7.0084404000000003E-2</v>
-      </c>
-      <c r="I27" s="10">
-        <v>15</v>
-      </c>
-      <c r="J27" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K27" s="9">
-        <v>10</v>
-      </c>
-      <c r="L27" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M27" s="9">
-        <v>35.671274310900891</v>
-      </c>
-      <c r="N27" s="9">
-        <v>15</v>
-      </c>
-      <c r="O27" s="9">
-        <v>1.0512660600000001</v>
-      </c>
-      <c r="P27" s="9">
-        <v>0.10512660600000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A28" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F28" s="8">
-        <v>5</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="9">
-        <v>6.7653344000000004E-2</v>
-      </c>
-      <c r="I28" s="10">
-        <v>15</v>
-      </c>
-      <c r="J28" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K28" s="9">
-        <v>10</v>
-      </c>
-      <c r="L28" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M28" s="9">
-        <v>36.953088379489415</v>
-      </c>
-      <c r="N28" s="9">
-        <v>15</v>
-      </c>
-      <c r="O28" s="9">
-        <v>1.0148001600000001</v>
-      </c>
-      <c r="P28" s="9">
-        <v>0.10148001600000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A29" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="8">
-        <v>6</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H29" s="9">
-        <v>6.4588591000000001E-2</v>
-      </c>
-      <c r="I29" s="10">
-        <v>15</v>
-      </c>
-      <c r="J29" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K29" s="9">
-        <v>10</v>
-      </c>
-      <c r="L29" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M29" s="9">
-        <v>38.706526358501918</v>
-      </c>
-      <c r="N29" s="9">
-        <v>15</v>
-      </c>
-      <c r="O29" s="9">
-        <v>0.96882886499999998</v>
-      </c>
-      <c r="P29" s="9">
-        <v>9.6882886500000001E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A30" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="8">
-        <v>4</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="P30" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A31" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="8">
-        <v>6</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H31" s="9">
-        <v>7.6975199999999994E-2</v>
-      </c>
-      <c r="I31" s="10">
-        <v>15</v>
-      </c>
-      <c r="J31" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K31" s="9">
-        <v>10</v>
-      </c>
-      <c r="L31" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M31" s="9">
-        <v>32.477992912002833</v>
-      </c>
-      <c r="N31" s="9">
-        <v>15</v>
-      </c>
-      <c r="O31" s="9">
-        <v>1.154628</v>
-      </c>
-      <c r="P31" s="9">
-        <v>0.1154628</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A32" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F32" s="8">
-        <v>6</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H32" s="9">
-        <v>7.5002561999999995E-2</v>
-      </c>
-      <c r="I32" s="10">
-        <v>15</v>
-      </c>
-      <c r="J32" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K32" s="9">
-        <v>10</v>
-      </c>
-      <c r="L32" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M32" s="9">
-        <v>33.332194705562195</v>
-      </c>
-      <c r="N32" s="9">
-        <v>15</v>
-      </c>
-      <c r="O32" s="9">
-        <v>1.12503843</v>
-      </c>
-      <c r="P32" s="9">
-        <v>0.11250384300000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A33" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="8">
-        <v>6</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H33" s="9">
-        <v>6.3006366999999994E-2</v>
-      </c>
-      <c r="I33" s="10">
-        <v>15</v>
-      </c>
-      <c r="J33" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K33" s="9">
-        <v>10</v>
-      </c>
-      <c r="L33" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M33" s="9">
-        <v>39.678529631775156</v>
-      </c>
-      <c r="N33" s="9">
-        <v>15</v>
-      </c>
-      <c r="O33" s="9">
-        <v>0.94509550499999995</v>
-      </c>
-      <c r="P33" s="9">
-        <v>9.4509550499999997E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A34" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="8">
-        <v>7</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H34" s="10">
-        <v>8.6226195000000005E-2</v>
-      </c>
-      <c r="I34" s="10">
-        <v>15</v>
-      </c>
-      <c r="J34" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K34" s="9">
-        <v>10</v>
-      </c>
-      <c r="L34" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M34" s="9">
-        <v>28.993509454986388</v>
-      </c>
-      <c r="N34" s="9">
-        <v>15</v>
-      </c>
-      <c r="O34" s="9">
-        <v>1.293392925</v>
-      </c>
-      <c r="P34" s="9">
-        <v>0.12933929250000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A35" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F35" s="8">
-        <v>7</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H35" s="10">
-        <v>3.6261878999999997E-2</v>
-      </c>
-      <c r="I35" s="10">
-        <v>15</v>
-      </c>
-      <c r="J35" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K35" s="9">
-        <v>10</v>
-      </c>
-      <c r="L35" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M35" s="9">
-        <v>68.942924882629498</v>
-      </c>
-      <c r="N35" s="9">
-        <v>15</v>
-      </c>
-      <c r="O35" s="9">
-        <v>0.54392818499999995</v>
-      </c>
-      <c r="P35" s="9">
-        <v>5.4392818499999995E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A36" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="8">
-        <v>7</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H36" s="10">
-        <v>4.8391554000000003E-2</v>
-      </c>
-      <c r="I36" s="10">
-        <v>15</v>
-      </c>
-      <c r="J36" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K36" s="9">
-        <v>10</v>
-      </c>
-      <c r="L36" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M36" s="9">
-        <v>51.661907778369752</v>
-      </c>
-      <c r="N36" s="9">
-        <v>15</v>
-      </c>
-      <c r="O36" s="9">
-        <v>0.7258733100000001</v>
-      </c>
-      <c r="P36" s="9">
-        <v>7.2587331000000005E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A37" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F37" s="8">
-        <v>7</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H37" s="10">
-        <v>4.6615635000000002E-2</v>
-      </c>
-      <c r="I37" s="10">
-        <v>15</v>
-      </c>
-      <c r="J37" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K37" s="9">
-        <v>10</v>
-      </c>
-      <c r="L37" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M37" s="9">
-        <v>53.63007497377221</v>
-      </c>
-      <c r="N37" s="9">
-        <v>15</v>
-      </c>
-      <c r="O37" s="9">
-        <v>0.69923452500000005</v>
-      </c>
-      <c r="P37" s="9">
-        <v>6.9923452500000011E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A38" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F38" s="8">
-        <v>5</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H38" s="9">
-        <v>4.9832737000000002E-2</v>
-      </c>
-      <c r="I38" s="10">
-        <v>15</v>
-      </c>
-      <c r="J38" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K38" s="9">
-        <v>10</v>
-      </c>
-      <c r="L38" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M38" s="9">
-        <v>50.167824416306892</v>
-      </c>
-      <c r="N38" s="9">
-        <v>15</v>
-      </c>
-      <c r="O38" s="9">
-        <v>0.74749105500000002</v>
-      </c>
-      <c r="P38" s="9">
-        <v>7.4749105499999996E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A39" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F39" s="8">
-        <v>7</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H39" s="10">
-        <v>0.155977693</v>
-      </c>
-      <c r="I39" s="10">
-        <v>15</v>
-      </c>
-      <c r="J39" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K39" s="9">
-        <v>10</v>
-      </c>
-      <c r="L39" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M39" s="9">
-        <v>16.027932917305041</v>
-      </c>
-      <c r="N39" s="9">
-        <v>15</v>
-      </c>
-      <c r="O39" s="9">
-        <v>2.3396653949999999</v>
-      </c>
-      <c r="P39" s="9">
-        <v>0.23396653949999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A40" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F40" s="8">
-        <v>8</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H40" s="10">
-        <v>0.34791216400000002</v>
-      </c>
-      <c r="I40" s="10">
-        <v>15</v>
-      </c>
-      <c r="J40" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K40" s="9">
-        <v>10</v>
-      </c>
-      <c r="L40" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M40" s="9">
-        <v>7.1857217386627497</v>
-      </c>
-      <c r="N40" s="9">
-        <v>7.1857217386627497</v>
-      </c>
-      <c r="O40" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P40" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A41" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" s="8">
-        <v>8</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H41" s="10">
-        <v>0.53156208800000004</v>
-      </c>
-      <c r="I41" s="10">
-        <v>15</v>
-      </c>
-      <c r="J41" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K41" s="9">
-        <v>10</v>
-      </c>
-      <c r="L41" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M41" s="9">
-        <v>4.7031194594901207</v>
-      </c>
-      <c r="N41" s="9">
-        <v>4.7031194594901207</v>
-      </c>
-      <c r="O41" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P41" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A42" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="8">
-        <v>9</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42" s="10">
-        <v>7.5254711000000002E-2</v>
-      </c>
-      <c r="I42" s="10">
-        <v>15</v>
-      </c>
-      <c r="J42" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K42" s="9">
-        <v>10</v>
-      </c>
-      <c r="L42" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M42" s="9">
-        <v>33.220511603585855</v>
-      </c>
-      <c r="N42" s="9">
-        <v>15</v>
-      </c>
-      <c r="O42" s="9">
-        <v>1.1288206650000001</v>
-      </c>
-      <c r="P42" s="9">
-        <v>0.11288206650000002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A43" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F43" s="8">
-        <v>9</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H43" s="10">
-        <v>5.4501832E-2</v>
-      </c>
-      <c r="I43" s="10">
-        <v>15</v>
-      </c>
-      <c r="J43" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K43" s="9">
-        <v>10</v>
-      </c>
-      <c r="L43" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M43" s="9">
-        <v>45.870017727110529</v>
-      </c>
-      <c r="N43" s="9">
-        <v>15</v>
-      </c>
-      <c r="O43" s="9">
-        <v>0.81752747999999997</v>
-      </c>
-      <c r="P43" s="9">
-        <v>8.1752748E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A44" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" s="8">
-        <v>9</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H44" s="10">
-        <v>2.6959294000000002E-2</v>
-      </c>
-      <c r="I44" s="10">
-        <v>15</v>
-      </c>
-      <c r="J44" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K44" s="9">
-        <v>10</v>
-      </c>
-      <c r="L44" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M44" s="9">
-        <v>92.732398704506124</v>
-      </c>
-      <c r="N44" s="9">
-        <v>15</v>
-      </c>
-      <c r="O44" s="9">
-        <v>0.40438941</v>
-      </c>
-      <c r="P44" s="9">
-        <v>4.0438940999999999E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A45" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F45" s="8">
-        <v>9</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H45" s="10">
-        <v>0.187221058</v>
-      </c>
-      <c r="I45" s="10">
-        <v>15</v>
-      </c>
-      <c r="J45" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K45" s="9">
-        <v>10</v>
-      </c>
-      <c r="L45" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M45" s="9">
-        <v>13.353198762502453</v>
-      </c>
-      <c r="N45" s="9">
-        <v>13.353198762502453</v>
-      </c>
-      <c r="O45" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P45" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A46" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="8">
-        <v>10</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="H46" s="10">
-        <v>8.9571618000000006E-2</v>
-      </c>
-      <c r="I46" s="10">
-        <v>15</v>
-      </c>
-      <c r="J46" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K46" s="9">
-        <v>10</v>
-      </c>
-      <c r="L46" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M46" s="9">
-        <v>27.910626779121035</v>
-      </c>
-      <c r="N46" s="9">
-        <v>15</v>
-      </c>
-      <c r="O46" s="9">
-        <v>1.3435742700000002</v>
-      </c>
-      <c r="P46" s="9">
-        <v>0.13435742700000003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A47" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" s="8">
-        <v>10</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H47" s="10">
-        <v>6.8883350999999995E-2</v>
-      </c>
-      <c r="I47" s="10">
-        <v>15</v>
-      </c>
-      <c r="J47" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K47" s="9">
-        <v>10</v>
-      </c>
-      <c r="L47" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M47" s="9">
-        <v>36.293240147390627</v>
-      </c>
-      <c r="N47" s="9">
-        <v>15</v>
-      </c>
-      <c r="O47" s="9">
-        <v>1.0332502649999999</v>
-      </c>
-      <c r="P47" s="9">
-        <v>0.1033250265</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A48" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="8">
-        <v>10</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="H48" s="10">
-        <v>0.14388271699999999</v>
-      </c>
-      <c r="I48" s="10">
-        <v>15</v>
-      </c>
-      <c r="J48" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K48" s="9">
-        <v>10</v>
-      </c>
-      <c r="L48" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M48" s="9">
-        <v>17.375262659239333</v>
-      </c>
-      <c r="N48" s="9">
-        <v>15</v>
-      </c>
-      <c r="O48" s="9">
-        <v>2.158240755</v>
-      </c>
-      <c r="P48" s="9">
-        <v>0.21582407549999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A49" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F49" s="8">
-        <v>6</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="N49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O49" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="P49" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A50" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="8">
-        <v>3</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H50" s="9">
-        <v>0.39906339200000002</v>
-      </c>
-      <c r="I50" s="10">
-        <v>15</v>
-      </c>
-      <c r="J50" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K50" s="9">
-        <v>10</v>
-      </c>
-      <c r="L50" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M50" s="9">
-        <v>6.2646688473995624</v>
-      </c>
-      <c r="N50" s="9">
-        <v>6.2646688473995624</v>
-      </c>
-      <c r="O50" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P50" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A51" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F51" s="8">
-        <v>3</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H51" s="9">
-        <v>0.144709797</v>
-      </c>
-      <c r="I51" s="10">
-        <v>15</v>
-      </c>
-      <c r="J51" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K51" s="9">
-        <v>10</v>
-      </c>
-      <c r="L51" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M51" s="9">
-        <v>17.275955407497392</v>
-      </c>
-      <c r="N51" s="9">
-        <v>15</v>
-      </c>
-      <c r="O51" s="9">
-        <v>2.170646955</v>
-      </c>
-      <c r="P51" s="9">
-        <v>0.21706469550000002</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A52" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F52" s="8">
-        <v>3</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H52" s="9">
-        <v>0.45730944299999998</v>
-      </c>
-      <c r="I52" s="10">
-        <v>15</v>
-      </c>
-      <c r="J52" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K52" s="9">
-        <v>10</v>
-      </c>
-      <c r="L52" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M52" s="9">
-        <v>5.466757877553821</v>
-      </c>
-      <c r="N52" s="9">
-        <v>5.466757877553821</v>
-      </c>
-      <c r="O52" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P52" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A53" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F53" s="8">
-        <v>4</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H53" s="9">
-        <v>0.28514014100000001</v>
-      </c>
-      <c r="I53" s="10">
-        <v>15</v>
-      </c>
-      <c r="J53" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K53" s="9">
-        <v>10</v>
-      </c>
-      <c r="L53" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M53" s="9">
-        <v>8.7676185865391716</v>
-      </c>
-      <c r="N53" s="9">
-        <v>8.7676185865391716</v>
-      </c>
-      <c r="O53" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P53" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A54" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F54" s="8">
-        <v>4</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H54" s="9">
-        <v>0.436762822</v>
-      </c>
-      <c r="I54" s="10">
-        <v>15</v>
-      </c>
-      <c r="J54" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K54" s="9">
-        <v>10</v>
-      </c>
-      <c r="L54" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M54" s="9">
-        <v>5.7239304127401214</v>
-      </c>
-      <c r="N54" s="9">
-        <v>5.7239304127401214</v>
-      </c>
-      <c r="O54" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P54" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A55" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="8">
-        <v>4</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H55" s="9">
-        <v>4.8891071000000001E-2</v>
-      </c>
-      <c r="I55" s="10">
-        <v>15</v>
-      </c>
-      <c r="J55" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K55" s="9">
-        <v>10</v>
-      </c>
-      <c r="L55" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M55" s="9">
-        <v>51.134081313129755</v>
-      </c>
-      <c r="N55" s="9">
-        <v>15</v>
-      </c>
-      <c r="O55" s="9">
-        <v>0.73336606500000001</v>
-      </c>
-      <c r="P55" s="9">
-        <v>7.3336606499999998E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A56" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F56" s="8">
-        <v>4</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H56" s="9">
-        <v>0.276154856</v>
-      </c>
-      <c r="I56" s="10">
-        <v>15</v>
-      </c>
-      <c r="J56" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K56" s="9">
-        <v>10</v>
-      </c>
-      <c r="L56" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M56" s="9">
-        <v>9.0528916862501241</v>
-      </c>
-      <c r="N56" s="9">
-        <v>9.0528916862501241</v>
-      </c>
-      <c r="O56" s="9">
-        <v>2.5000000000000004</v>
-      </c>
-      <c r="P56" s="9">
-        <v>0.25000000000000006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A57" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F57" s="8">
-        <v>4</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H57" s="9">
-        <v>0.37032288299999999</v>
-      </c>
-      <c r="I57" s="10">
-        <v>15</v>
-      </c>
-      <c r="J57" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K57" s="9">
-        <v>10</v>
-      </c>
-      <c r="L57" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M57" s="9">
-        <v>6.7508655683046195</v>
-      </c>
-      <c r="N57" s="9">
-        <v>6.7508655683046195</v>
-      </c>
-      <c r="O57" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P57" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A58" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F58" s="8">
-        <v>5</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H58" s="9">
-        <v>0.61326692400000005</v>
-      </c>
-      <c r="I58" s="10">
-        <v>15</v>
-      </c>
-      <c r="J58" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K58" s="9">
-        <v>10</v>
-      </c>
-      <c r="L58" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M58" s="9">
-        <v>4.0765283470595257</v>
-      </c>
-      <c r="N58" s="9">
-        <v>4.0765283470595257</v>
-      </c>
-      <c r="O58" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P58" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A59" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F59" s="8">
-        <v>5</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H59" s="9">
-        <v>0.61956045800000004</v>
-      </c>
-      <c r="I59" s="10">
-        <v>15</v>
-      </c>
-      <c r="J59" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K59" s="9">
-        <v>10</v>
-      </c>
-      <c r="L59" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M59" s="9">
-        <v>4.0351187163723088</v>
-      </c>
-      <c r="N59" s="9">
-        <v>4.0351187163723088</v>
-      </c>
-      <c r="O59" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P59" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A60" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F60" s="8">
-        <v>5</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H60" s="9">
-        <v>0.124925095</v>
-      </c>
-      <c r="I60" s="10">
-        <v>15</v>
-      </c>
-      <c r="J60" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K60" s="9">
-        <v>10</v>
-      </c>
-      <c r="L60" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M60" s="9">
-        <v>20.011991986077739</v>
-      </c>
-      <c r="N60" s="9">
-        <v>15</v>
-      </c>
-      <c r="O60" s="9">
-        <v>1.873876425</v>
-      </c>
-      <c r="P60" s="9">
-        <v>0.18738764250000001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A61" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F61" s="8">
-        <v>8</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="N61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O61" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="P61" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A62" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F62" s="8">
-        <v>6</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H62" s="9">
-        <v>0.170897725</v>
-      </c>
-      <c r="I62" s="10">
-        <v>15</v>
-      </c>
-      <c r="J62" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K62" s="9">
-        <v>10</v>
-      </c>
-      <c r="L62" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M62" s="9">
-        <v>14.628632417429781</v>
-      </c>
-      <c r="N62" s="9">
-        <v>14.628632417429781</v>
-      </c>
-      <c r="O62" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P62" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A63" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F63" s="8">
-        <v>6</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H63" s="9">
-        <v>0.28168763499999999</v>
-      </c>
-      <c r="I63" s="10">
-        <v>15</v>
-      </c>
-      <c r="J63" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K63" s="9">
-        <v>10</v>
-      </c>
-      <c r="L63" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M63" s="9">
-        <v>8.8750789504835748</v>
-      </c>
-      <c r="N63" s="9">
-        <v>8.8750789504835748</v>
-      </c>
-      <c r="O63" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="P63" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A64" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F64" s="8">
-        <v>6</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H64" s="9">
-        <v>0.11297718900000001</v>
-      </c>
-      <c r="I64" s="10">
-        <v>15</v>
-      </c>
-      <c r="J64" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K64" s="9">
-        <v>10</v>
-      </c>
-      <c r="L64" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M64" s="9">
-        <v>22.128360796797661</v>
-      </c>
-      <c r="N64" s="9">
-        <v>15</v>
-      </c>
-      <c r="O64" s="9">
-        <v>1.6946578350000001</v>
-      </c>
-      <c r="P64" s="9">
-        <v>0.16946578350000002</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A65" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="8">
-        <v>7</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H65" s="10">
-        <v>4.4094234000000003E-2</v>
-      </c>
-      <c r="I65" s="10">
-        <v>15</v>
-      </c>
-      <c r="J65" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K65" s="9">
-        <v>10</v>
-      </c>
-      <c r="L65" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M65" s="9">
-        <v>56.696755407974656</v>
-      </c>
-      <c r="N65" s="9">
-        <v>15</v>
-      </c>
-      <c r="O65" s="9">
-        <v>0.66141351000000004</v>
-      </c>
-      <c r="P65" s="9">
-        <v>6.6141351000000001E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A66" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F66" s="8">
-        <v>7</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H66" s="10">
-        <v>3.9138421E-2</v>
-      </c>
-      <c r="I66" s="10">
-        <v>15</v>
-      </c>
-      <c r="J66" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K66" s="9">
-        <v>10</v>
-      </c>
-      <c r="L66" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M66" s="9">
-        <v>63.875852324241698</v>
-      </c>
-      <c r="N66" s="9">
-        <v>15</v>
-      </c>
-      <c r="O66" s="9">
-        <v>0.58707631500000002</v>
-      </c>
-      <c r="P66" s="9">
-        <v>5.8707631500000003E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A67" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F67" s="8">
-        <v>7</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H67" s="10">
-        <v>1.7511714000000001E-2</v>
-      </c>
-      <c r="I67" s="10">
-        <v>15</v>
-      </c>
-      <c r="J67" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K67" s="9">
-        <v>10</v>
-      </c>
-      <c r="L67" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M67" s="9">
-        <v>142.76158233283161</v>
-      </c>
-      <c r="N67" s="9">
-        <v>15</v>
-      </c>
-      <c r="O67" s="9">
-        <v>0.26267571000000001</v>
-      </c>
-      <c r="P67" s="9">
-        <v>2.6267571E-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A68" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="8">
-        <v>8</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H68" s="10">
-        <v>3.2586165E-2</v>
-      </c>
-      <c r="I68" s="10">
-        <v>15</v>
-      </c>
-      <c r="J68" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K68" s="9">
-        <v>10</v>
-      </c>
-      <c r="L68" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M68" s="9">
-        <v>76.719675359159325</v>
-      </c>
-      <c r="N68" s="9">
-        <v>15</v>
-      </c>
-      <c r="O68" s="9">
-        <v>0.488792475</v>
-      </c>
-      <c r="P68" s="9">
-        <v>4.88792475E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A69" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F69" s="8">
-        <v>8</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H69" s="10">
-        <v>2.0341366999999999E-2</v>
-      </c>
-      <c r="I69" s="10">
-        <v>15</v>
-      </c>
-      <c r="J69" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K69" s="9">
-        <v>10</v>
-      </c>
-      <c r="L69" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M69" s="9">
-        <v>122.90226119021402</v>
-      </c>
-      <c r="N69" s="9">
-        <v>15</v>
-      </c>
-      <c r="O69" s="9">
-        <v>0.30512050499999999</v>
-      </c>
-      <c r="P69" s="9">
-        <v>3.0512050499999999E-2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A70" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F70" s="8">
-        <v>8</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H70" s="10">
-        <v>2.0191770000000001E-2</v>
-      </c>
-      <c r="I70" s="10">
-        <v>15</v>
-      </c>
-      <c r="J70" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K70" s="9">
-        <v>10</v>
-      </c>
-      <c r="L70" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M70" s="9">
-        <v>123.81282076806539</v>
-      </c>
-      <c r="N70" s="9">
-        <v>15</v>
-      </c>
-      <c r="O70" s="9">
-        <v>0.30287655000000002</v>
-      </c>
-      <c r="P70" s="9">
-        <v>3.0287655000000004E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A71" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="8">
-        <v>8</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H71" s="10">
-        <v>3.0158490999999999E-2</v>
-      </c>
-      <c r="I71" s="10">
-        <v>15</v>
-      </c>
-      <c r="J71" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K71" s="9">
-        <v>10</v>
-      </c>
-      <c r="L71" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M71" s="9">
-        <v>82.895394202581286</v>
-      </c>
-      <c r="N71" s="9">
-        <v>15</v>
-      </c>
-      <c r="O71" s="9">
-        <v>0.45237736499999998</v>
-      </c>
-      <c r="P71" s="9">
-        <v>4.52377365E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A72" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F72" s="8">
-        <v>6</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="K72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="N72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O72" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="P72" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A73" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F73" s="8">
-        <v>8</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H73" s="10">
-        <v>3.8249560000000002E-2</v>
-      </c>
-      <c r="I73" s="10">
-        <v>15</v>
-      </c>
-      <c r="J73" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K73" s="9">
-        <v>10</v>
-      </c>
-      <c r="L73" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M73" s="9">
-        <v>65.360228980411804</v>
-      </c>
-      <c r="N73" s="9">
-        <v>15</v>
-      </c>
-      <c r="O73" s="9">
-        <v>0.57374340000000001</v>
-      </c>
-      <c r="P73" s="9">
-        <v>5.7374340000000003E-2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A74" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F74" s="8">
-        <v>10</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="K74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="N74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O74" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="P74" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A75" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" s="8">
-        <v>9</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H75" s="10">
-        <v>2.6414114999999998E-2</v>
-      </c>
-      <c r="I75" s="10">
-        <v>15</v>
-      </c>
-      <c r="J75" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K75" s="9">
-        <v>10</v>
-      </c>
-      <c r="L75" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M75" s="9">
-        <v>94.646366156882408</v>
-      </c>
-      <c r="N75" s="9">
-        <v>15</v>
-      </c>
-      <c r="O75" s="9">
-        <v>0.39621172499999996</v>
-      </c>
-      <c r="P75" s="9">
-        <v>3.9621172499999996E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A76" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" s="8">
-        <v>9</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H76" s="10">
-        <v>2.6492190999999998E-2</v>
-      </c>
-      <c r="I76" s="10">
-        <v>15</v>
-      </c>
-      <c r="J76" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K76" s="9">
-        <v>10</v>
-      </c>
-      <c r="L76" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M76" s="9">
-        <v>94.367430764786505</v>
-      </c>
-      <c r="N76" s="9">
-        <v>15</v>
-      </c>
-      <c r="O76" s="9">
-        <v>0.39738286499999997</v>
-      </c>
-      <c r="P76" s="9">
-        <v>3.9738286499999997E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A77" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" s="8">
-        <v>9</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H77" s="10">
-        <v>2.4088343000000002E-2</v>
-      </c>
-      <c r="I77" s="10">
-        <v>15</v>
-      </c>
-      <c r="J77" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K77" s="9">
-        <v>10</v>
-      </c>
-      <c r="L77" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M77" s="9">
-        <v>103.78463973217252</v>
-      </c>
-      <c r="N77" s="9">
-        <v>15</v>
-      </c>
-      <c r="O77" s="9">
-        <v>0.36132514500000001</v>
-      </c>
-      <c r="P77" s="9">
-        <v>3.6132514500000004E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A78" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F78" s="8">
-        <v>10</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H78" s="10">
-        <v>5.7928014E-2</v>
-      </c>
-      <c r="I78" s="10">
-        <v>15</v>
-      </c>
-      <c r="J78" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K78" s="9">
-        <v>10</v>
-      </c>
-      <c r="L78" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M78" s="9">
-        <v>43.15701208054535</v>
-      </c>
-      <c r="N78" s="9">
-        <v>15</v>
-      </c>
-      <c r="O78" s="9">
-        <v>0.86892020999999997</v>
-      </c>
-      <c r="P78" s="9">
-        <v>8.6892021E-2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A79" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F79" s="8">
-        <v>10</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H79" s="10">
-        <v>6.7471015999999995E-2</v>
-      </c>
-      <c r="I79" s="10">
-        <v>15</v>
-      </c>
-      <c r="J79" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K79" s="9">
-        <v>10</v>
-      </c>
-      <c r="L79" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M79" s="9">
-        <v>37.052947298140587</v>
-      </c>
-      <c r="N79" s="9">
-        <v>15</v>
-      </c>
-      <c r="O79" s="9">
-        <v>1.0120652399999999</v>
-      </c>
-      <c r="P79" s="9">
-        <v>0.10120652399999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.75">
-      <c r="A80" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F80" s="8">
-        <v>10</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H80" s="10">
-        <v>9.0132157000000004E-2</v>
-      </c>
-      <c r="I80" s="10">
-        <v>15</v>
-      </c>
-      <c r="J80" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="K80" s="9">
-        <v>10</v>
-      </c>
-      <c r="L80" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="M80" s="9">
-        <v>27.737048387735797</v>
-      </c>
-      <c r="N80" s="9">
-        <v>15</v>
-      </c>
-      <c r="O80" s="9">
-        <v>1.3519823550000001</v>
-      </c>
-      <c r="P80" s="9">
-        <v>0.13519823550000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.75">
-      <c r="A81" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F81" s="8">
-        <v>10</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="J81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="K81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="M81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="N81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="O81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="P81" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q81" s="17">
-        <f>MIN(P2:P81)</f>
-        <v>2.6036590500000002E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.75">
-      <c r="Q82" s="17">
-        <f>MAX(P2:P81)</f>
-        <v>0.25000000000000006</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:Q82" xr:uid="{E10C50BE-D82B-4376-8B52-5947BC365404}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="buffer tl"/>
-        <filter val="cold storage"/>
-        <filter val="dess"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:Q80">
-      <sortCondition ref="D1:D82"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43DBCD1-F7D4-4327-A88E-EE1A6C48ABC1}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
-  <cols>
-    <col min="1" max="1" width="6.5" style="1" customWidth="1"/>
-    <col min="2" max="13" width="9.31640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="B1" s="11" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="B2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="B3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A4" s="12"/>
-      <c r="B4" s="8">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8">
-        <v>2</v>
-      </c>
-      <c r="D4" s="8">
-        <v>3</v>
-      </c>
-      <c r="E4" s="8">
-        <v>4</v>
-      </c>
-      <c r="F4" s="8">
-        <v>5</v>
-      </c>
-      <c r="G4" s="8">
-        <v>6</v>
-      </c>
-      <c r="H4" s="8">
-        <v>7</v>
-      </c>
-      <c r="I4" s="8">
-        <v>8</v>
-      </c>
-      <c r="J4" s="8">
-        <v>9</v>
-      </c>
-      <c r="K4" s="8">
-        <v>10</v>
-      </c>
-      <c r="L4" s="8">
-        <v>11</v>
-      </c>
-      <c r="M4" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A10" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.75">
-      <c r="A12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>